--- a/portfolio_holdings.xlsx
+++ b/portfolio_holdings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tevajanura/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tevajanura/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA4BDC9-072E-7947-A0FD-8C211F681847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39442CB3-0520-8741-88A8-2495D9838915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="14960" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="40">
   <si>
     <t>Ticker</t>
   </si>
@@ -147,6 +147,15 @@
   </si>
   <si>
     <t>KAP.IL</t>
+  </si>
+  <si>
+    <t>SCATC.OL</t>
+  </si>
+  <si>
+    <t>MDT</t>
+  </si>
+  <si>
+    <t>LTH</t>
   </si>
 </sst>
 </file>
@@ -304,7 +313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -320,6 +329,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -622,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53818241-40AE-A54F-AD2D-BA33D2294ACE}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -1274,6 +1289,141 @@
         <v>144.97999999999999</v>
       </c>
     </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="15">
+        <v>46153</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="17">
+        <v>947</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="15">
+        <v>46153</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="20">
+        <v>845</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="15">
+        <v>46153</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="17">
+        <v>5433</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="15">
+        <v>46153</v>
+      </c>
+      <c r="B33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="20">
+        <v>7765</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="15">
+        <v>46146</v>
+      </c>
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" s="17">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="15">
+        <v>46139</v>
+      </c>
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="20">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="15">
+        <v>46139</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="17">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="15">
+        <v>46139</v>
+      </c>
+      <c r="B37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="20">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="15">
+        <v>46139</v>
+      </c>
+      <c r="B38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="17">
+        <v>3861</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/portfolio_holdings.xlsx
+++ b/portfolio_holdings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tevajanura/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39442CB3-0520-8741-88A8-2495D9838915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF54485-9F98-EB4B-9FAE-290922C37B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="14960" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="40">
   <si>
     <t>Ticker</t>
   </si>
@@ -313,7 +313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -330,11 +330,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1302,7 +1301,7 @@
       <c r="D30" s="17">
         <v>947</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="12" t="s">
         <v>25</v>
       </c>
       <c r="F30" t="s">
@@ -1316,13 +1315,13 @@
       <c r="B31" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="20">
+      <c r="C31" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="19">
         <v>845</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="12" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1340,21 +1339,24 @@
         <v>5433</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="15">
         <v>46153</v>
       </c>
       <c r="B33" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D33" s="20">
+      <c r="C33" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="19">
         <v>7765</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E33" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="15">
         <v>46146</v>
       </c>
@@ -1367,22 +1369,25 @@
       <c r="D34" s="17">
         <v>760</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E34" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="15">
         <v>46139</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="20">
+      <c r="C35" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="19">
         <v>644</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="15">
         <v>46139</v>
       </c>
@@ -1396,21 +1401,21 @@
         <v>344</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="15">
         <v>46139</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
       </c>
-      <c r="C37" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="20">
+      <c r="C37" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="19">
         <v>444</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="15">
         <v>46139</v>
       </c>
@@ -1422,6 +1427,9 @@
       </c>
       <c r="D38" s="17">
         <v>3861</v>
+      </c>
+      <c r="E38" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
